--- a/samples/excel/試用資料_含錯誤.xlsx
+++ b/samples/excel/試用資料_含錯誤.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19820" uniqueCount="1962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19820" uniqueCount="1963">
   <si>
     <t xml:space="preserve">申報資料檢核助手｜試用資料（含錯誤）</t>
   </si>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">P250003601     </t>
   </si>
   <si>
-    <t xml:space="preserve">19450410</t>
+    <t xml:space="preserve">18550301</t>
   </si>
   <si>
     <t xml:space="preserve">20050317</t>
@@ -4054,7 +4054,7 @@
     <t xml:space="preserve">20250322</t>
   </si>
   <si>
-    <t xml:space="preserve">000000000601234500</t>
+    <t xml:space="preserve">20210413</t>
   </si>
   <si>
     <t xml:space="preserve">W19  </t>
@@ -12440,6 +12440,9 @@
     <t xml:space="preserve">P250002201     </t>
   </si>
   <si>
+    <t xml:space="preserve">19450410</t>
+  </si>
+  <si>
     <t xml:space="preserve">P250005901     </t>
   </si>
   <si>
@@ -13448,7 +13451,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">25702_L4103</t>
+    <t xml:space="preserve">X002</t>
   </si>
   <si>
     <t xml:space="preserve">P250003601/A01</t>
@@ -13460,7 +13463,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">躉繳</t>
+      <t xml:space="preserve">被保險人投保年齡 </t>
     </r>
     <r>
       <rPr>
@@ -13469,7 +13472,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(0)</t>
+      <t xml:space="preserve">150 </t>
     </r>
     <r>
       <rPr>
@@ -13477,7 +13480,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">卻填繳費期間 </t>
+      <t xml:space="preserve">歲 </t>
     </r>
     <r>
       <rPr>
@@ -13486,23 +13489,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">020</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">L4403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250003701/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">職業類別 </t>
+      <t xml:space="preserve">出生日期誤植</t>
     </r>
     <r>
       <rPr>
@@ -13511,15 +13506,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8(</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">L4403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250003701/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">拒保</t>
+      <t xml:space="preserve">職業類別 </t>
     </r>
     <r>
       <rPr>
@@ -13528,7 +13531,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">8(</t>
     </r>
     <r>
       <rPr>
@@ -13536,7 +13539,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但職業分類代碼不為 </t>
+      <t xml:space="preserve">拒保</t>
     </r>
     <r>
       <rPr>
@@ -13545,23 +13548,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">24602_L2703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004001/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">) </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">身障等級 </t>
+      <t xml:space="preserve">但職業分類代碼不為 </t>
     </r>
     <r>
       <rPr>
@@ -13570,15 +13565,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
+      <t xml:space="preserve">0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">24602_L2703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004001/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但身障類別 </t>
+      <t xml:space="preserve">身障等級 </t>
     </r>
     <r>
       <rPr>
@@ -13587,23 +13590,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">000</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">25002_L1233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004301/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">2 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">次標準體原因</t>
+      <t xml:space="preserve">但身障類別 </t>
     </r>
     <r>
       <rPr>
@@ -13612,15 +13607,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">=1 </t>
-    </r>
+      <t xml:space="preserve">000</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25002_L1233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004301/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但體檢類別</t>
+      <t xml:space="preserve">次標準體原因</t>
     </r>
     <r>
       <rPr>
@@ -13629,7 +13632,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">=1(</t>
+      <t xml:space="preserve">=1 </t>
     </r>
     <r>
       <rPr>
@@ -13637,7 +13640,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">標準體</t>
+      <t xml:space="preserve">但體檢類別</t>
     </r>
     <r>
       <rPr>
@@ -13646,23 +13649,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">24701_L4501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004401/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">=1(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">新契約要保人郵遞區號填 </t>
+      <t xml:space="preserve">標準體</t>
     </r>
     <r>
       <rPr>
@@ -13671,14 +13666,14 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">999</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">22300_L4602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004701/A01</t>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">24701_L4501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004401/A01</t>
   </si>
   <si>
     <r>
@@ -13687,7 +13682,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">被保險人郵遞區號 </t>
+      <t xml:space="preserve">新契約要保人郵遞區號填 </t>
     </r>
     <r>
       <rPr>
@@ -13696,31 +13691,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">000 </t>
-    </r>
+      <t xml:space="preserve">999</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">22300_L4602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004701/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不存在</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">25304_L2106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004901/A01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定期壽險還本型態填 </t>
+      <t xml:space="preserve">被保險人郵遞區號 </t>
     </r>
     <r>
       <rPr>
@@ -13729,23 +13716,31 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">25805_L4202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004101/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">000 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">停效但停</t>
+      <t xml:space="preserve">不存在</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25304_L2106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004901/A01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定期壽險還本型態填 </t>
     </r>
     <r>
       <rPr>
@@ -13754,15 +13749,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25805_L4202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004101/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">失</t>
+      <t xml:space="preserve">停效但停</t>
     </r>
     <r>
       <rPr>
@@ -13771,7 +13774,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -13779,7 +13782,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">效原因填 </t>
+      <t xml:space="preserve">失</t>
     </r>
     <r>
       <rPr>
@@ -13788,23 +13791,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">N</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">26104_L1504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250007501/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">)</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">退保別 </t>
+      <t xml:space="preserve">效原因填 </t>
     </r>
     <r>
       <rPr>
@@ -13813,15 +13808,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">XED </t>
-    </r>
+      <t xml:space="preserve">N</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">26104_L1504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250007501/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但退保日期不為 </t>
+      <t xml:space="preserve">退保別 </t>
     </r>
     <r>
       <rPr>
@@ -13830,32 +13833,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10400_L3701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250005301/A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公司保單險種代號含全形字</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30301_LD012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250002301/A01</t>
-  </si>
-  <si>
+      <t xml:space="preserve">XED </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">疾病死亡</t>
+      <t xml:space="preserve">但退保日期不為 </t>
     </r>
     <r>
       <rPr>
@@ -13864,40 +13850,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(DEA)</t>
-    </r>
+      <t xml:space="preserve">0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10400_L3701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250005301/A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公司保單險種代號含全形字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30301_LD012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250002301/A01</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">但給付檔漏報</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">30312_LD019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250004601/A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">給付發生日期與承保退保日期不一致</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24101_D1303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P250003001/A01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實際給付金額不同但不同原因填 </t>
+      <t xml:space="preserve">疾病死亡</t>
     </r>
     <r>
       <rPr>
@@ -13906,7 +13884,66 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">(DEA)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">但給付檔漏報</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">30312_LD019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250004601/A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">給付發生日期與承保退保日期不一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26600_D1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P250003001/A01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理賠發生日期早於保險期間起日 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">承保退保日期未同步，連帶 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30312_LD019)</t>
     </r>
   </si>
   <si>
@@ -25086,10 +25123,10 @@
         <v>147</v>
       </c>
       <c r="AP49" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AQ49" s="8" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="AR49" s="8" t="s">
         <v>110</v>
@@ -45230,13 +45267,13 @@
         <v>398</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>397</v>
+        <v>973</v>
       </c>
       <c r="P7" s="8" t="s">
         <v>910</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>964</v>
@@ -45275,7 +45312,7 @@
         <v>910</v>
       </c>
       <c r="AD7" s="8" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="AE7" s="8" t="s">
         <v>967</v>
@@ -61382,7 +61419,7 @@
         <v>316</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>440</v>
+        <v>1636</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>101</v>
@@ -65243,7 +65280,7 @@
         <v>91</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>93</v>
@@ -65300,10 +65337,10 @@
         <v>319</v>
       </c>
       <c r="U56" s="8" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="V56" s="8" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="W56" s="8" t="s">
         <v>101</v>
@@ -65378,10 +65415,10 @@
         <v>106</v>
       </c>
       <c r="AU56" s="8" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="AV56" s="8" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="AW56" s="8" t="s">
         <v>180</v>
@@ -65411,7 +65448,7 @@
         <v>102</v>
       </c>
       <c r="BF56" s="8" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="BG56" s="8" t="s">
         <v>123</v>
@@ -65822,7 +65859,7 @@
         <v>125</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="K59" s="8" t="s">
         <v>101</v>
@@ -66377,7 +66414,7 @@
         <v>125</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="K62" s="8" t="s">
         <v>102</v>
@@ -74863,7 +74900,7 @@
         <v>91</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>93</v>
@@ -75073,36 +75110,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="E2" s="11" t="n">
         <v>1</v>
@@ -75113,16 +75150,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E3" s="11" t="n">
         <v>1</v>
@@ -75133,16 +75170,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>1</v>
@@ -75153,16 +75190,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>1</v>
@@ -75173,16 +75210,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>2</v>
@@ -75193,16 +75230,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>2</v>
@@ -75213,16 +75250,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>1</v>
@@ -75233,16 +75270,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>2</v>
@@ -75253,16 +75290,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>6</v>
@@ -75273,16 +75310,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>3</v>
@@ -75293,16 +75330,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>3</v>
@@ -75313,16 +75350,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>2</v>
@@ -75333,16 +75370,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>2</v>
@@ -75353,36 +75390,36 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>16012345</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>1</v>
@@ -75393,16 +75430,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>1660</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1659</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>1</v>
@@ -75413,16 +75450,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>77</v>
@@ -75433,16 +75470,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>1</v>
@@ -75453,16 +75490,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>2</v>
@@ -75473,16 +75510,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>2</v>
@@ -75493,16 +75530,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>2</v>
@@ -75513,16 +75550,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>1</v>
@@ -75533,16 +75570,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>2</v>
@@ -75553,16 +75590,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
@@ -75573,16 +75610,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>1</v>
@@ -75593,16 +75630,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>2</v>
@@ -75637,22 +75674,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75660,7 +75697,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="C2" s="14" t="n">
         <f aca="false">SUM(C3,C7,C10,C14,C17,C19)</f>
@@ -75681,10 +75718,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C3" s="12" t="n">
         <f aca="false">SUM(C4,C5,C6)</f>
@@ -75705,10 +75742,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="C4" s="17" t="n">
         <v>4498391000</v>
@@ -75725,10 +75762,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>7687712000</v>
@@ -75745,10 +75782,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>7322105000</v>
@@ -75768,7 +75805,7 @@
         <v>1627</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="C7" s="12" t="n">
         <f aca="false">SUM(C8,C9)</f>
@@ -75789,10 +75826,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C8" s="17" t="n">
         <v>2580566000</v>
@@ -75809,10 +75846,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>7297425000</v>
@@ -75832,7 +75869,7 @@
         <v>1620</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">SUM(C11,C12,C13)</f>
@@ -75853,10 +75890,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>1197217000</v>
@@ -75873,10 +75910,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>1387088000</v>
@@ -75893,10 +75930,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>5319308000</v>
@@ -75916,7 +75953,7 @@
         <v>1615</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">SUM(C15,C16)</f>
@@ -75937,10 +75974,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>3562234000</v>
@@ -75957,10 +75994,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="C16" s="17" t="n">
         <v>8875646000</v>
@@ -75977,10 +76014,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">SUM(C18)</f>
@@ -76001,10 +76038,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>1707</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>1706</v>
       </c>
       <c r="C18" s="17" t="n">
         <v>6314526000</v>
@@ -76021,10 +76058,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">SUM(C20)</f>
@@ -76045,10 +76082,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C20" s="17" t="n">
         <v>8481199000</v>
@@ -76068,7 +76105,7 @@
         <v>102</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">SUM(C22,C26,C33)</f>
@@ -76076,11 +76113,11 @@
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">SUM(D22,D26,D33)</f>
-        <v>1937271345</v>
+        <v>1937259000</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">SUM(E22,E26,E33)</f>
-        <v>2686184345</v>
+        <v>2686172000</v>
       </c>
       <c r="F21" s="14" t="n">
         <f aca="false">SUM(F22,F26,F33)</f>
@@ -76089,10 +76126,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUM(C23,C24,C25)</f>
@@ -76100,11 +76137,11 @@
       </c>
       <c r="D22" s="12" t="n">
         <f aca="false">SUM(D23,D24,D25)</f>
-        <v>587814345</v>
+        <v>587802000</v>
       </c>
       <c r="E22" s="12" t="n">
         <f aca="false">SUM(E23,E24,E25)</f>
-        <v>919762345</v>
+        <v>919750000</v>
       </c>
       <c r="F22" s="12" t="n">
         <f aca="false">SUM(F23,F24,F25)</f>
@@ -76113,19 +76150,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>4235000</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>71196345</v>
+        <v>71184000</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>68962345</v>
+        <v>68950000</v>
       </c>
       <c r="F23" s="17" t="n">
         <v>6469000</v>
@@ -76133,10 +76170,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="C24" s="17" t="n">
         <v>2886063000</v>
@@ -76153,10 +76190,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C25" s="17" t="n">
         <v>1365499000</v>
@@ -76173,10 +76210,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">SUM(C27,C28,C29,C30,C31,C32)</f>
@@ -76197,10 +76234,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C27" s="17" t="n">
         <v>2211344000</v>
@@ -76217,10 +76254,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C28" s="17" t="n">
         <v>3110749000</v>
@@ -76237,10 +76274,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>2908040000</v>
@@ -76257,10 +76294,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C30" s="17" t="n">
         <v>3220369000</v>
@@ -76277,10 +76314,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="C31" s="17" t="n">
         <v>2317717000</v>
@@ -76297,10 +76334,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="C32" s="17" t="n">
         <v>209514000</v>
@@ -76317,10 +76354,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="C33" s="12" t="n">
         <f aca="false">SUM(C34)</f>
@@ -76341,10 +76378,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>1737</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>1736</v>
       </c>
       <c r="C34" s="17" t="n">
         <v>1713256000</v>
@@ -76364,7 +76401,7 @@
         <v>143</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="C35" s="14" t="n">
         <f aca="false">SUM(C36,C38,C42)</f>
@@ -76385,10 +76422,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C36" s="12" t="n">
         <f aca="false">SUM(C37)</f>
@@ -76409,10 +76446,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="C37" s="17" t="n">
         <v>435496000</v>
@@ -76429,10 +76466,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">SUM(C39,C40,C41)</f>
@@ -76453,10 +76490,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>800641000</v>
@@ -76473,10 +76510,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="C40" s="17" t="n">
         <v>581211000</v>
@@ -76493,10 +76530,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="C41" s="17" t="n">
         <v>42183176000</v>
@@ -76513,10 +76550,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="C42" s="12" t="n">
         <f aca="false">SUM(C43)</f>
@@ -76537,10 +76574,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="C43" s="17" t="n">
         <v>576107000</v>
@@ -76584,750 +76621,750 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>32</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>34</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>38</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>10</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>49</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>55</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>63</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>65</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>56</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>95</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>33</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>66</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>76</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>8</v>
@@ -77335,15 +77372,15 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
@@ -77351,7 +77388,7 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77359,19 +77396,19 @@
         <v>14</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>78</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77379,19 +77416,19 @@
         <v>14</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>93</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77399,17 +77436,17 @@
         <v>12</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77417,17 +77454,17 @@
         <v>12</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77435,17 +77472,17 @@
         <v>12</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77453,17 +77490,17 @@
         <v>12</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77471,17 +77508,17 @@
         <v>12</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77489,19 +77526,19 @@
         <v>12</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>44</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77509,17 +77546,17 @@
         <v>12</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77527,19 +77564,19 @@
         <v>12</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77547,19 +77584,19 @@
         <v>12</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77567,19 +77604,19 @@
         <v>12</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>16</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -77587,359 +77624,359 @@
         <v>12</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>24</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>110</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>109</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>31</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="10" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="10" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>20</v>
@@ -77949,43 +77986,43 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
   </sheetData>

--- a/samples/excel/試用資料_含錯誤.xlsx
+++ b/samples/excel/試用資料_含錯誤.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="承保資料" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="給付資料" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="保單資料" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="理賠資料" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="客戶資料" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="商品資料" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="上年度承保資料" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="控制總數" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="去年保單資料" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="系統總數" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="資產負債表" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="錯誤解答" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">上年度承保資料!$A$1:$BI$108</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">保單資料!$A$1:$BI$154</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">去年保單資料!$A$1:$BI$108</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">商品資料!$A$1:$G$15</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">客戶資料!$A$1:$I$240</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">承保資料!$A$1:$BI$154</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">給付資料!$A$1:$AE$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">理賠資料!$A$1:$AE$32</definedName>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">錯誤解答!$A$1:$F$73</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19820" uniqueCount="1963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19820" uniqueCount="1962">
   <si>
     <t xml:space="preserve">申報資料檢核助手｜試用資料（含錯誤）</t>
   </si>
@@ -67,11 +67,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">檔整個拖進任一上傳格，工具會依工作表名稱自動分配到各檔案。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本檔刻意放入各類錯誤與差異，解答在「錯誤解答」工作表；試用時可先不看解答，比對工具找到的結果。</t>
+      <t xml:space="preserve">檔拖進上方的大框，工具會依工作表名稱自動分好。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本檔刻意放入各種錯誤，答案在「錯誤解答」工作表；試用時可先不看答案，比對工具找到的結果。</t>
   </si>
   <si>
     <r>
@@ -80,7 +80,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">欄位：承保／給付／上年度資料的欄位依《人壽保險業個人壽險填報手冊》</t>
+      <t xml:space="preserve">欄位：保單、理賠、去年保單資料的欄位依《人壽保險業個人壽險填報手冊》</t>
     </r>
     <r>
       <rPr>
@@ -114,7 +114,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；數字欄位以文字儲存，保留前置 </t>
+      <t xml:space="preserve">；數字以文字儲存，保留開頭的 </t>
     </r>
     <r>
       <rPr>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">內容</t>
   </si>
   <si>
-    <t xml:space="preserve">承保資料</t>
+    <t xml:space="preserve">保單資料</t>
   </si>
   <si>
     <r>
@@ -153,7 +153,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">保單資料（承保檔 </t>
+      <t xml:space="preserve">每張保單的申報資料（</t>
     </r>
     <r>
       <rPr>
@@ -162,7 +162,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">LFL</t>
+      <t xml:space="preserve">61 </t>
     </r>
     <r>
       <rPr>
@@ -170,7 +170,20 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">欄）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">理賠資料</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每筆理賠給付的申報資料（</t>
     </r>
     <r>
       <rPr>
@@ -179,7 +192,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">61 </t>
+      <t xml:space="preserve">31 </t>
     </r>
     <r>
       <rPr>
@@ -191,7 +204,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">給付資料</t>
+    <t xml:space="preserve">客戶資料</t>
   </si>
   <si>
     <r>
@@ -200,7 +213,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">理賠資料（給付檔 </t>
+      <t xml:space="preserve">要保人（角色 </t>
     </r>
     <r>
       <rPr>
@@ -209,7 +222,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">LFD</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -217,7 +230,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
+      <t xml:space="preserve">）與被保險人（角色 </t>
     </r>
     <r>
       <rPr>
@@ -226,7 +239,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">31 </t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -234,11 +247,35 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">欄）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">客戶資料</t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">商品資料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商品代號、險種、繳費年期、起售日、停售日、替代代號</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去年保單資料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去年申報的保單資料，用來確認去年底和今年初接得上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系統總數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新契約、理賠、保單系統各自的筆數與金額總數，用來核對申報資料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資產負債表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">各科目餘額，上層科目用公式加總</t>
+  </si>
+  <si>
+    <t xml:space="preserve">錯誤解答</t>
   </si>
   <si>
     <r>
@@ -247,7 +284,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">要保人（角色 </t>
+      <t xml:space="preserve">刻意放入的錯誤和工具應找到的結果（含 </t>
     </r>
     <r>
       <rPr>
@@ -256,7 +293,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">4 </t>
     </r>
     <r>
       <rPr>
@@ -264,78 +301,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）與被保險人（角色 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">商品資料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商品代號、險種、繳費年期、起售日、停售日、替代代號</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上年度承保資料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上年度申報檔，用於期初／期末結轉勾稽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">控制總數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新契約、理賠、保單管理系統的控制總數，用於跨系統對帳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資產負債表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">科目餘額（含準備金），上層科目為公式加總</t>
-  </si>
-  <si>
-    <t xml:space="preserve">錯誤解答</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">刻意放入的錯誤與預期的檢核結果（含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">筆「疑似異常（需人工判斷）」的合理性案例）</t>
+      <t xml:space="preserve">筆「請人工判斷」的不太合理案例）</t>
     </r>
   </si>
   <si>
@@ -433,7 +399,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">注意：承保資料檔中「長度不足」的一筆與「空白行」無法以 </t>
+      <t xml:space="preserve">注意：保單資料文字檔中「長度不足」的一筆與「空白行」無法在 </t>
     </r>
     <r>
       <rPr>
@@ -452,7 +418,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">儲存格表示，請使用 </t>
+      <t xml:space="preserve">中表示，請用 </t>
     </r>
     <r>
       <rPr>
@@ -490,7 +456,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">因此不在本檔「承保資料」，客戶資料會連帶出現 </t>
+      <t xml:space="preserve">因此不在本檔「保單資料」，客戶資料會連帶出現 </t>
     </r>
     <r>
       <rPr>
@@ -12916,7 +12882,7 @@
     <t xml:space="preserve">類別</t>
   </si>
   <si>
-    <t xml:space="preserve">檢核編號</t>
+    <t xml:space="preserve">規則編號</t>
   </si>
   <si>
     <t xml:space="preserve">保單號碼／科目／期間</t>
@@ -12946,7 +12912,7 @@
     <t xml:space="preserve">說明</t>
   </si>
   <si>
-    <t xml:space="preserve">明細檢核</t>
+    <t xml:space="preserve">保單／理賠資料</t>
   </si>
   <si>
     <t xml:space="preserve">23900_L0802</t>
@@ -14556,7 +14522,7 @@
     <t xml:space="preserve">身份為本人，但要保人與被保險人證號不同</t>
   </si>
   <si>
-    <t xml:space="preserve">疑似異常（需人工判斷）</t>
+    <t xml:space="preserve">請人工判斷（不太合理）</t>
   </si>
   <si>
     <t xml:space="preserve">A001</t>
@@ -14605,7 +14571,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）（不是錯誤：結果應標為疑似異常，由人工判斷）</t>
+      <t xml:space="preserve">）（不算錯誤：工具會標成「請人工判斷」）</t>
     </r>
   </si>
   <si>
@@ -14638,7 +14604,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（不是錯誤：結果應標為疑似異常，由人工判斷）</t>
+      <t xml:space="preserve">（不算錯誤：工具會標成「請人工判斷」）</t>
     </r>
   </si>
   <si>
@@ -14697,7 +14663,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）疾病身故（不是錯誤：結果應標為疑似異常，由人工判斷）</t>
+      <t xml:space="preserve">）疾病身故（不算錯誤：工具會標成「請人工判斷」）</t>
     </r>
   </si>
   <si>
@@ -14781,17 +14747,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）身故給付（不是錯誤：結果應標為疑似異常，由人工判斷）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">匯入規則</t>
+      <t xml:space="preserve">）身故給付（不算錯誤：工具會標成「請人工判斷」）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自訂規則</t>
   </si>
   <si>
     <t xml:space="preserve">U002</t>
   </si>
   <si>
-    <t xml:space="preserve">承保資料／給付資料</t>
+    <t xml:space="preserve">保單資料／理賠資料</t>
   </si>
   <si>
     <t xml:space="preserve">P250006201/A01</t>
@@ -14820,7 +14786,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">歲承保終身壽險（需先在「規則匯入」套用公司內部核保規則）</t>
+      <t xml:space="preserve">歲承保終身壽險（需先在「新增檢查規則」套用範例的公司內部規則）</t>
     </r>
   </si>
   <si>
@@ -14853,7 +14819,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">萬元未體檢（需先在「規則匯入」套用公司內部核保規則）</t>
+      <t xml:space="preserve">萬元未體檢（需先在「新增檢查規則」套用範例的公司內部規則）</t>
     </r>
   </si>
   <si>
@@ -14886,11 +14852,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">天才給付（需先在「規則匯入」套用公司內部核保規則）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">期初期末結轉</t>
+      <t xml:space="preserve">天才給付（需先在「新增檢查規則」套用範例的公司內部規則）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">去年和今年</t>
   </si>
   <si>
     <t xml:space="preserve">P004</t>
@@ -15027,7 +14993,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">跨系統對帳</t>
+    <t xml:space="preserve">和系統總數比對</t>
   </si>
   <si>
     <t xml:space="preserve">R001</t>
@@ -15068,7 +15034,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月（應判定為：時間差）</t>
+      <t xml:space="preserve">月（應判定為：結帳日不同）</t>
     </r>
   </si>
   <si>
@@ -15115,7 +15081,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（應判定為：時間差）</t>
+      <t xml:space="preserve">（應判定為：結帳日不同）</t>
     </r>
   </si>
   <si>
@@ -15188,14 +15154,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（應判定為：時間差）</t>
+      <t xml:space="preserve">（應判定為：結帳日不同）</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">INF 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">保單管理系統外幣保單以原幣加總（應判定為：定義差）</t>
+    <t xml:space="preserve">保單管理系統外幣保單以原幣加總（應判定為：算法不同）</t>
   </si>
   <si>
     <t xml:space="preserve">NB 2025-03</t>
@@ -15241,11 +15207,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">萬元，申報漏報（應判定為：待查）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">財報勾稽</t>
+      <t xml:space="preserve">萬元，申報漏報（應判定為：需要追查）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">S008</t>
@@ -15920,7 +15883,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">COUNTA(承保資料!A:A)-1</f>
+        <f aca="false">COUNTA(保單資料!A:A)-1</f>
         <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -15932,7 +15895,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <f aca="false">COUNTA(給付資料!A:A)-1</f>
+        <f aca="false">COUNTA(理賠資料!A:A)-1</f>
         <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -15968,7 +15931,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="n">
-        <f aca="false">COUNTA(上年度承保資料!A:A)-1</f>
+        <f aca="false">COUNTA(去年保單資料!A:A)-1</f>
         <v>107</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -15980,7 +15943,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="n">
-        <f aca="false">COUNTA(控制總數!A:A)-1</f>
+        <f aca="false">COUNTA(系統總數!A:A)-1</f>
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -77937,10 +77900,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69" s="10" t="s">
         <v>1952</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>1953</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>20</v>
@@ -77950,15 +77913,15 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>1952</v>
+        <v>20</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>20</v>
@@ -77968,15 +77931,15 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>1952</v>
+        <v>20</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>20</v>
@@ -77986,15 +77949,15 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>1952</v>
+        <v>20</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>20</v>
@@ -78004,15 +77967,15 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>1952</v>
+        <v>20</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>20</v>
@@ -78022,7 +77985,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
   </sheetData>
